--- a/data/trans_bre/MCS12_SP_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R3-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,48</t>
+          <t>2,05; 9,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 13,73</t>
+          <t>6,01; 14,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 16,98</t>
+          <t>8,11; 16,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 16,6</t>
+          <t>7,38; 16,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 38,42</t>
+          <t>6,93; 36,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 49,79</t>
+          <t>18,54; 51,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,18; 70,4</t>
+          <t>29,02; 71,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,8; 67,56</t>
+          <t>24,72; 65,47</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 11,07</t>
+          <t>5,37; 11,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,41</t>
+          <t>6,28; 12,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,1</t>
+          <t>2,82; 8,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 35,83</t>
+          <t>6,17; 34,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,83; 84,61</t>
+          <t>33,51; 83,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,87; 63,89</t>
+          <t>27,81; 62,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 51,13</t>
+          <t>15,36; 51,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,13; 286,89</t>
+          <t>34,67; 260,29</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 11,12</t>
+          <t>1,25; 11,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,38</t>
+          <t>2,78; 13,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 9,04</t>
+          <t>0,06; 9,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 8,16</t>
+          <t>-1,68; 8,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 84,55</t>
+          <t>6,74; 89,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,19; 130,26</t>
+          <t>16,93; 123,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 69,63</t>
+          <t>-0,38; 73,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 46,84</t>
+          <t>-7,21; 48,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,95</t>
+          <t>5,94; 9,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 12,62</t>
+          <t>8,47; 12,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,94</t>
+          <t>5,92; 9,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 27,8</t>
+          <t>7,59; 26,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 56,06</t>
+          <t>29,99; 56,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,78; 59,51</t>
+          <t>36,45; 60,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,47; 55,36</t>
+          <t>29,82; 54,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,38; 169,87</t>
+          <t>37,77; 162,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R3-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,89</t>
+          <t>13,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 9,23</t>
+          <t>1,89; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,01; 14,15</t>
+          <t>6,23; 14,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 16,99</t>
+          <t>8,14; 17,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 16,38</t>
+          <t>9,0; 17,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 36,41</t>
+          <t>6,15; 37,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,54; 51,97</t>
+          <t>19,18; 52,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,02; 71,5</t>
+          <t>27,63; 71,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,72; 65,47</t>
+          <t>29,31; 74,38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,29</t>
+          <t>5,8; 11,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 12,1</t>
+          <t>6,86; 12,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,11</t>
+          <t>2,89; 8,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 34,15</t>
+          <t>3,85; 9,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,51; 83,19</t>
+          <t>36,7; 87,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,81; 62,09</t>
+          <t>30,59; 61,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,36; 51,29</t>
+          <t>15,58; 52,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,67; 260,29</t>
+          <t>19,39; 54,45</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>5,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,64</t>
+          <t>2,08; 12,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 13,32</t>
+          <t>3,04; 13,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 9,52</t>
+          <t>-0,16; 9,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 8,34</t>
+          <t>1,56; 9,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 89,91</t>
+          <t>10,86; 93,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,93; 123,56</t>
+          <t>19,58; 126,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 73,21</t>
+          <t>-1,21; 67,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 48,79</t>
+          <t>7,16; 55,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,61</t>
+          <t>8,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 9,87</t>
+          <t>5,82; 9,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 12,67</t>
+          <t>8,17; 12,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,89</t>
+          <t>5,84; 9,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 26,56</t>
+          <t>6,36; 10,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,99; 56,25</t>
+          <t>29,39; 56,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,45; 60,75</t>
+          <t>34,77; 58,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,82; 54,99</t>
+          <t>29,58; 56,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,77; 162,42</t>
+          <t>31,03; 54,09</t>
         </is>
       </c>
     </row>
